--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_demografia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13671,7 +13671,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18409,7 +18409,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20068,7 +20068,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -21016,7 +21016,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21411,7 +21411,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21725,7 +21725,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21962,7 +21962,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22436,7 +22436,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22515,7 +22515,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23542,7 +23542,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23700,7 +23700,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25754,7 +25754,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25833,7 +25833,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25912,7 +25912,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26465,7 +26465,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26623,7 +26623,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26700,7 +26700,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26856,7 +26856,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27409,7 +27409,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27567,7 +27567,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27725,7 +27725,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -28120,7 +28120,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28436,7 +28436,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28752,7 +28752,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -29068,7 +29068,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29463,7 +29463,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29779,7 +29779,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -30095,7 +30095,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30253,7 +30253,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30332,7 +30332,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30569,7 +30569,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30885,7 +30885,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -31043,7 +31043,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31201,7 +31201,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31675,7 +31675,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31754,7 +31754,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32386,7 +32386,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32702,7 +32702,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -33097,7 +33097,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33413,7 +33413,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33571,7 +33571,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33650,7 +33650,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33887,7 +33887,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -34045,7 +34045,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34124,7 +34124,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34361,7 +34361,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34677,7 +34677,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34756,7 +34756,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -35072,7 +35072,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35230,7 +35230,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35388,7 +35388,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35467,7 +35467,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35704,7 +35704,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35783,7 +35783,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35862,7 +35862,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -36020,7 +36020,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36257,7 +36257,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36494,7 +36494,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36731,7 +36731,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36810,7 +36810,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36889,7 +36889,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36968,7 +36968,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -37047,7 +37047,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37205,7 +37205,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37284,7 +37284,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37363,7 +37363,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37442,7 +37442,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37679,7 +37679,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37837,7 +37837,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37995,7 +37995,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -38074,7 +38074,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38153,7 +38153,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38469,7 +38469,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38548,7 +38548,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38785,7 +38785,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38864,7 +38864,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38943,7 +38943,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -39022,7 +39022,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -39101,7 +39101,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39180,7 +39180,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39259,7 +39259,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39338,7 +39338,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39575,7 +39575,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39654,7 +39654,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39812,7 +39812,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39970,7 +39970,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40128,7 +40128,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40444,7 +40444,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40918,7 +40918,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -41076,7 +41076,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41313,7 +41313,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41392,7 +41392,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41471,7 +41471,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41550,7 +41550,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41708,7 +41708,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41787,7 +41787,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41866,7 +41866,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42182,7 +42182,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42261,7 +42261,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42340,7 +42340,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
